--- a/Demo.xlsx
+++ b/Demo.xlsx
@@ -57,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -353,111 +354,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1">
         <v>101</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1">
+        <v>46060</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>102</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="1">
+        <v>46061</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>103</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" s="1">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>104</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" s="1">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
+      <c r="C5" s="1">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
+      <c r="C6" s="1">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>107</v>
       </c>
       <c r="B7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
+      <c r="C7" s="1">
+        <v>46066</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>108</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
+      <c r="C8" s="1">
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>109</v>
       </c>
       <c r="B9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:2">
+      <c r="C9" s="1">
+        <v>46068</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>110</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
+      <c r="C10" s="1">
+        <v>46069</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>111</v>
       </c>
       <c r="B11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:2">
+      <c r="C11" s="1">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>112</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
+      <c r="C12" s="1">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>113</v>
       </c>
       <c r="B13" t="s">
         <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46072</v>
       </c>
     </row>
   </sheetData>
